--- a/documentation/markdown/SFRA-ChangeLog.xlsx
+++ b/documentation/markdown/SFRA-ChangeLog.xlsx
@@ -1,19 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{736124EF-AA95-47F4-AF7C-7D5131DD5A82}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_A4CF39A909A50ABF4FF1355DF3C240045AAD5333" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{D35E8B8D-89CA-134E-A396-1F2A36F310C9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -22,6 +33,15 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="71">
   <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>File Name</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
     <t>M</t>
   </si>
   <si>
@@ -221,15 +241,6 @@
   </si>
   <si>
     <t>new XSD file for updated cybersource endpoint</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
-    <t>File Name</t>
-  </si>
-  <si>
-    <t>Description</t>
   </si>
   <si>
     <t>configuration/PayerAuth-Meta.xml</t>
@@ -239,7 +250,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -638,419 +649,419 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55EF33EC-A479-F64B-84E8-50A1622500DC}">
   <dimension ref="A1:C38"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="6.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="113.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="75.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="31.5">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="31.5">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="126">
+      <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="31.5">
+      <c r="A7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="31.5">
+      <c r="A8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="31.5">
+      <c r="A9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="31.5">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="31.5">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="31.5">
+      <c r="A12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="31.5">
+      <c r="A14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="31.5">
+      <c r="A15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="31.5">
+      <c r="A16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="31.5">
+      <c r="A17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="157.5">
+      <c r="A19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="157.5">
+      <c r="A20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="31.5">
+      <c r="A21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="31.5">
+      <c r="A22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="31.5">
+      <c r="A23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="31.5">
+      <c r="A24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="63">
+      <c r="A25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="78.75">
+      <c r="A26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="47.25">
+      <c r="A27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="31.5">
+      <c r="A31" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="31.5">
+      <c r="A33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="31.5">
+      <c r="A34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="5" t="s">
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C36" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="126" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="2" t="s">
+    <row r="37" spans="1:3">
+      <c r="A37" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="157.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="157.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="63" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>70</v>
       </c>
       <c r="C37" s="1"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -1058,4 +1069,316 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1fc7c887-ecc2-48fb-8824-1f2f117491b4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0a2ccfb7-4253-4103-bb4d-66c5ddba3bad" xsi:nil="true"/>
+    <Test xmlns="1fc7c887-ecc2-48fb-8824-1f2f117491b4" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F49D4C8C253F4A41A5A5F678468DAC0C" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="158857f20439908f202f2e896e6abbdc">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="1fc7c887-ecc2-48fb-8824-1f2f117491b4" xmlns:ns3="8e05cebd-4d68-49e9-b516-24759e7b5315" xmlns:ns4="0a2ccfb7-4253-4103-bb4d-66c5ddba3bad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="186aea8cace3489082424aefed17b49a" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
+    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
+    <xsd:import namespace="1fc7c887-ecc2-48fb-8824-1f2f117491b4"/>
+    <xsd:import namespace="8e05cebd-4d68-49e9-b516-24759e7b5315"/>
+    <xsd:import namespace="0a2ccfb7-4253-4103-bb4d-66c5ddba3bad"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:Test" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns4:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
+                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="26" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="27" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="1fc7c887-ecc2-48fb-8824-1f2f117491b4" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="18" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Test" ma:index="19" nillable="true" ma:displayName="Test" ma:internalName="Test">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="726df4c0-9ee9-406c-8b5c-a0fe24c95ff8" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="24" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="25" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e05cebd-4d68-49e9-b516-24759e7b5315" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="0a2ccfb7-4253-4103-bb4d-66c5ddba3bad" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{60cf621c-88e6-40bd-8926-6b55d23d48cf}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="ab57723f-2061-4a38-853d-8af9704a4d97">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD3F276D-B62C-4BF6-89B2-AA4685DAC13E}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9F62525-CF61-480C-8749-BAE6A459BE20}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C22A5554-5B97-4CF6-AC96-8A9BB536EDB7}"/>
 </file>